--- a/plantillas/46.xlsx
+++ b/plantillas/46.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$2</definedName>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/46.xlsx
+++ b/plantillas/46.xlsx
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/46.xlsx
+++ b/plantillas/46.xlsx
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
